--- a/data/trans_orig/IP07C04-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07C04-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse  alegre en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores según la frecuencia de sentirse alegre en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29156</t>
+          <t>29218</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38574</t>
+          <t>38428</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24113</t>
+          <t>24224</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33974</t>
+          <t>33665</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55895</t>
+          <t>56378</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69590</t>
+          <t>69769</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,83%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11560</t>
+          <t>12060</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7544</t>
+          <t>7833</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17237</t>
+          <t>17102</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13544</t>
+          <t>13862</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26817</t>
+          <t>25997</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4241</t>
+          <t>4116</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>636</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>642</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5810</t>
+          <t>5764</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>108569</t>
+          <t>109990</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>130626</t>
+          <t>131545</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,82 +1429,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>69,09%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>142585</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>130895</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>153343</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>65,61%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>60,23%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>70,56%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>394</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>262972</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>247942</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>279727</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>64,5%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>60,82%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>68,61%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>142585</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>130327</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>153656</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>65,61%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>59,97%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>70,71%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>262972</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>247889</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>278401</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>64,5%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>60,8%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>68,29%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54551</t>
+          <t>53584</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75421</t>
+          <t>74426</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55830</t>
+          <t>56295</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78573</t>
+          <t>78381</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>115885</t>
+          <t>115103</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>145167</t>
+          <t>145845</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,77%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2465</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>10167</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11580</t>
+          <t>12165</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7745</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18842</t>
+          <t>18825</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2702</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4167</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3380</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23519</t>
+          <t>23574</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35186</t>
+          <t>35560</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27455</t>
+          <t>27416</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38252</t>
+          <t>38010</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54853</t>
+          <t>54328</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69985</t>
+          <t>70366</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>68,13%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15198</t>
+          <t>15039</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>26532</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7783</t>
+          <t>8267</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18528</t>
+          <t>18327</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26157</t>
+          <t>26399</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40704</t>
+          <t>41366</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>40,05%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2086</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9160</t>
+          <t>9281</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6141</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11173</t>
+          <t>11301</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>4799</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>3892</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>170150</t>
+          <t>170576</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>196009</t>
+          <t>196528</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>190615</t>
+          <t>190652</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>218211</t>
+          <t>216814</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>370417</t>
+          <t>369016</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>406483</t>
+          <t>407370</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,95%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>79425</t>
+          <t>79514</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>105345</t>
+          <t>104771</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>78752</t>
+          <t>79270</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>105381</t>
+          <t>105305</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>166387</t>
+          <t>165532</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>200674</t>
+          <t>203662</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,97%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7375</t>
+          <t>6662</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18540</t>
+          <t>17557</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5905</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15366</t>
+          <t>15742</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15428</t>
+          <t>14748</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29392</t>
+          <t>30268</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>642</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>610</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>5667</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9322</t>
+          <t>9740</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4636</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4364</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse  alegre en 2012 (tasa de respuesta: 95,72%)</t>
+          <t>Menores según la frecuencia de sentirse alegre en 2012 (tasa de respuesta: 95,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23932</t>
+          <t>23497</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35474</t>
+          <t>35041</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20384</t>
+          <t>20646</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31501</t>
+          <t>31941</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47319</t>
+          <t>47875</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63686</t>
+          <t>64668</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>66,81%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14948</t>
+          <t>14445</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26598</t>
+          <t>26706</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11590</t>
+          <t>11475</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22629</t>
+          <t>22345</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29519</t>
+          <t>29283</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45750</t>
+          <t>45943</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,47%</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4866</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>644</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5747</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3487</t>
+          <t>3244</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3410</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4313</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3432</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>101291</t>
+          <t>102057</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>125118</t>
+          <t>124899</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>127328</t>
+          <t>127665</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>150377</t>
+          <t>151278</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>234928</t>
+          <t>236435</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>268653</t>
+          <t>269569</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>63,5%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65582</t>
+          <t>65101</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88326</t>
+          <t>88574</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66393</t>
+          <t>64912</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89030</t>
+          <t>87926</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>137613</t>
+          <t>136745</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>170149</t>
+          <t>169865</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,01%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3559</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12187</t>
+          <t>12097</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11916</t>
+          <t>12726</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8948</t>
+          <t>9383</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20764</t>
+          <t>21122</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>615</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7960</t>
+          <t>6790</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>7267</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>3749</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32801</t>
+          <t>33030</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45498</t>
+          <t>45374</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27619</t>
+          <t>26763</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39318</t>
+          <t>38923</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>63927</t>
+          <t>63006</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>80139</t>
+          <t>80354</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,71%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12030</t>
+          <t>12003</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23691</t>
+          <t>23665</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14814</t>
+          <t>14427</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26189</t>
+          <t>26613</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29757</t>
+          <t>30205</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46535</t>
+          <t>46686</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,92%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>590</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5207</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>568</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1836</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8592</t>
+          <t>8418</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>3643</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>603</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5925</t>
+          <t>5746</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>594</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5374</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>166874</t>
+          <t>167795</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>196520</t>
+          <t>195597</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>184999</t>
+          <t>184673</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>214121</t>
+          <t>213243</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>360633</t>
+          <t>360857</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>401399</t>
+          <t>399760</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,63%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>101589</t>
+          <t>102227</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>129609</t>
+          <t>129177</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>100156</t>
+          <t>100268</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>127306</t>
+          <t>127819</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>209276</t>
+          <t>209638</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>249816</t>
+          <t>248068</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>38,87%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5907</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16892</t>
+          <t>16443</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>5514</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16218</t>
+          <t>15229</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13806</t>
+          <t>14226</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27886</t>
+          <t>27675</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>680</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>7026</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9523</t>
+          <t>9644</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>592</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse  alegre en 2016 (tasa de respuesta: 95,77%)</t>
+          <t>Menores según la frecuencia de sentirse alegre en 2016 (tasa de respuesta: 95,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13315</t>
+          <t>13370</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22122</t>
+          <t>22010</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15115</t>
+          <t>14910</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24903</t>
+          <t>25007</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30874</t>
+          <t>31391</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44393</t>
+          <t>44511</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,19%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7449</t>
+          <t>7162</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16085</t>
+          <t>16186</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10545</t>
+          <t>10486</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>20797</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20601</t>
+          <t>20479</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33483</t>
+          <t>33710</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>50,13%</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>563</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>134522</t>
+          <t>133773</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>160124</t>
+          <t>159428</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>131288</t>
+          <t>129812</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>157029</t>
+          <t>155767</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>272370</t>
+          <t>270623</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>307709</t>
+          <t>308661</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>64,16%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72086</t>
+          <t>73218</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>97355</t>
+          <t>98209</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71242</t>
+          <t>71934</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96113</t>
+          <t>97022</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>151166</t>
+          <t>151319</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>186831</t>
+          <t>187345</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,94%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6471</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17506</t>
+          <t>17514</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13570</t>
+          <t>13322</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13101</t>
+          <t>13694</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27234</t>
+          <t>27965</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>4146</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4582</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5487</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32653</t>
+          <t>32245</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46994</t>
+          <t>46553</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40647</t>
+          <t>40519</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54399</t>
+          <t>55093</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>78294</t>
+          <t>77182</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97671</t>
+          <t>98124</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,94%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21728</t>
+          <t>21995</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35687</t>
+          <t>35851</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20458</t>
+          <t>19706</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34170</t>
+          <t>34284</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45707</t>
+          <t>46146</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65584</t>
+          <t>66790</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>45,56%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>632</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>6336</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2704</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7006</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>190271</t>
+          <t>190265</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>220194</t>
+          <t>221744</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>195433</t>
+          <t>195551</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>228045</t>
+          <t>226418</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>397743</t>
+          <t>393387</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>438420</t>
+          <t>437515</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>62,96%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>109131</t>
+          <t>109274</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>139562</t>
+          <t>138798</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>110181</t>
+          <t>112032</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>141961</t>
+          <t>140237</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>230910</t>
+          <t>229674</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>270385</t>
+          <t>273356</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,34%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9637</t>
+          <t>9570</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21850</t>
+          <t>22042</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15565</t>
+          <t>15331</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>17358</t>
+          <t>17328</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>33692</t>
+          <t>34720</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -9040,7 +9040,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4534</t>
+          <t>3838</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4920</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>724</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07C04-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07C04-Estudios-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse alegre en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores según la frecuencia de sentirse alegre, percibida por el/la menor [KIDSCREEN 20] en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>29269</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>23645</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>33992</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>67,71%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>54,7%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>78,64%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>33989</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>29218</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>38428</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>29055</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>38144</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>75,06%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>64,52%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>84,86%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>29269</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>24224</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>33665</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>67,71%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56378</t>
+          <t>56031</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69769</t>
+          <t>69596</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,63%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11983</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7494</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17222</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>27,72%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>17,34%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>39,84%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>7386</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3914</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>12060</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3991</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>12128</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>16,31%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>26,63%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>11983</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>7833</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>17102</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>27,72%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13862</t>
+          <t>13508</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25997</t>
+          <t>26300</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,71%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1358</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4411</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,14%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>10,21%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1979</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5211</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>4,37%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>1,41%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,51%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1358</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>4116</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>7323</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2526</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,84%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1931</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5183</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5187</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,26%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>1,4%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,44%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3140</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>5770</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>43224</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>43224</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>43224</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>45285</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>45285</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>45285</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>43224</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>43224</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>43224</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>142585</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>132236</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>153099</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>65,61%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>60,85%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>70,45%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>179</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>120387</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>109990</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>131545</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>109639</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>130965</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>63,23%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>57,77%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>69,09%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>142585</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>130895</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>153343</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>65,61%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>247942</t>
+          <t>247476</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>279727</t>
+          <t>277824</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,14%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>66437</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>56263</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>77274</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>30,57%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>25,89%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>35,56%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>64278</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>53584</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>74426</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>53833</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>74897</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>33,76%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>28,15%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>39,09%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>66437</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>56295</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>78381</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>115103</t>
+          <t>115858</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>145845</t>
+          <t>146394</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,91%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6946</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3607</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>11887</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5,47%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>5184</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2529</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>10167</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2463</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>9335</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>2,72%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,34%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>6946</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>3716</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>12165</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7180</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18825</t>
+          <t>18441</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -1748,102 +1748,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3224</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>537</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2715</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2676</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1216</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4434</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4295</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1216</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4258</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -1856,107 +1856,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3358</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>667</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4096</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>3995</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3309</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>217314</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>217314</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>217314</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>190386</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>190386</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>190386</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>217314</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>217314</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>217314</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>33164</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>27403</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>38147</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>67,63%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>55,88%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>77,79%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>29407</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>23574</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>35560</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>23202</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>35629</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>54,21%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>43,46%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>65,55%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>33164</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>27416</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>38010</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>67,63%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54328</t>
+          <t>54613</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70366</t>
+          <t>70367</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>12913</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>8678</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>18687</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>26,33%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>17,7%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>38,11%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>20333</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>15039</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>26532</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>14974</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>26380</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>37,48%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>27,72%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>48,91%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>12913</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>8267</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>18327</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>26,33%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26399</t>
+          <t>26003</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41366</t>
+          <t>41228</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,92%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5160</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,06%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>10,52%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>4506</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>2086</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>9281</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1631</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>8709</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>8,31%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>17,11%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>1503</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>4586</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2924</t>
+          <t>2893</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>11135</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -2425,107 +2425,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3978</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>8,11%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>802</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3955</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4011</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>8,07%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>802</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4799</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -2538,107 +2538,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3951</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>8,06%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>659</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>3892</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>3339</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>7,94%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>659</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>3329</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>49040</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>49040</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>49040</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>54246</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>54246</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>54246</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>49040</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>49040</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>49040</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2768,72 +2768,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>205018</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>190016</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>217178</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>66,22%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>61,38%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>70,15%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>183783</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>170576</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>196528</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>169690</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>196086</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>63,39%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>58,84%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>67,79%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>205018</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>190652</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>216814</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>66,22%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>369016</t>
+          <t>370382</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>407370</t>
+          <t>407239</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,93%</t>
         </is>
       </c>
     </row>
@@ -2886,67 +2886,67 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>91333</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>78848</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>104928</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>29,5%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>25,47%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>33,89%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
           <t>91996</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>79514</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>104771</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>80044</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>105687</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>31,73%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>27,43%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>36,14%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>91333</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>79270</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>105305</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>29,5%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>165532</t>
+          <t>165606</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>203662</t>
+          <t>201023</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -2994,72 +2994,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>9807</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>5695</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>15145</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>11669</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>6662</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>17557</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>7709</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>18638</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>4,03%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>9807</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>5700</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>15742</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14748</t>
+          <t>15194</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>30268</t>
+          <t>29875</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -3107,72 +3107,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2095</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>6787</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>2467</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>6175</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>6324</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,85%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,22%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>2095</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>5667</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9740</t>
+          <t>9045</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -3220,107 +3220,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>4655</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>1325</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>4630</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>4001</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1325</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>4655</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -3333,57 +3333,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>309578</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>309578</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>309578</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>431</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>289916</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>289916</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>289916</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>466</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>309578</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>309578</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>309578</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3496,13 +3496,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse alegre en 2012 (tasa de respuesta: 95,72%)</t>
+          <t>Menores según la frecuencia de sentirse alegre, percibida por el/la menor [KIDSCREEN 20] en 2012 (tasa de respuesta: 95,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3513,7 +3513,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3681,72 +3681,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>26167</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>20473</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>31842</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>57,94%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>45,33%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>70,51%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>29860</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>23497</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>35041</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>23879</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>35856</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>57,84%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>45,51%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>67,88%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>26167</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>20646</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>31941</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>57,94%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47875</t>
+          <t>48075</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64668</t>
+          <t>64062</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,19%</t>
         </is>
       </c>
     </row>
@@ -3794,72 +3794,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16897</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11227</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22325</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>37,42%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>24,86%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>49,43%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>20373</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14445</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>26706</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>14502</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>26425</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>39,46%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>27,98%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>51,73%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>16897</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>11475</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22345</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>37,42%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29283</t>
+          <t>29715</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45943</t>
+          <t>45243</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>46,74%</t>
         </is>
       </c>
     </row>
@@ -3907,72 +3907,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2710</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>6,0%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1392</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5588</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4878</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>2,7%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>10,82%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>3357</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>652</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>5769</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -4020,107 +4020,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3150</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,98%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>624</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3244</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>7,18%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3774</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -4133,107 +4133,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4156</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>9,2%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>823</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4313</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3367</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>9,55%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>823</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4069</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -4246,57 +4246,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>45162</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>45162</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>45162</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>51626</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>51626</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>51626</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>45162</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>45162</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>45162</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4363,72 +4363,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>139295</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>126711</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>150239</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>61,97%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>56,37%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>66,84%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>113288</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>102057</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>124899</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>101723</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>124715</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>56,72%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>51,09%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>62,53%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>139295</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>127665</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>151278</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>61,97%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>236435</t>
+          <t>237696</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>269569</t>
+          <t>271421</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,94%</t>
         </is>
       </c>
     </row>
@@ -4476,72 +4476,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>77049</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>65580</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>88518</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>34,28%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>29,18%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>39,38%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>76886</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>65101</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>88574</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>65638</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>87754</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>38,49%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>32,59%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>44,34%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>77049</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>64912</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>87926</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>34,28%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>136745</t>
+          <t>136382</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>169865</t>
+          <t>169672</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,97%</t>
         </is>
       </c>
     </row>
@@ -4589,72 +4589,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7216</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3904</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>12354</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>6775</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3191</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>12097</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>3411</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>11924</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>3,39%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>7216</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>3826</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>12726</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9383</t>
+          <t>8969</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>21122</t>
+          <t>20351</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -4702,72 +4702,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3332</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2798</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>615</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6790</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6994</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,4%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>580</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3062</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7267</t>
+          <t>7779</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -4815,107 +4815,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3477</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>625</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3749</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4087</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3351</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -4928,57 +4928,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>224765</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>224765</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>224765</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>199748</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>199748</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>199748</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>224765</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>224765</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>224765</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5045,72 +5045,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>33369</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>26916</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>59,43%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>47,93%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>70,23%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>39158</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>33030</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>45374</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>32498</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>44862</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>64,4%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>54,32%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>74,63%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>33369</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>26763</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>38923</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>59,43%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>63006</t>
+          <t>63307</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>80354</t>
+          <t>80741</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>69,04%</t>
         </is>
       </c>
     </row>
@@ -5158,72 +5158,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>20072</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>13891</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>25745</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>35,75%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>24,74%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>45,85%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>17614</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>12003</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>23665</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>12219</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>24430</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>28,97%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>19,74%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>38,92%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>20072</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>14427</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>26613</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>35,75%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30205</t>
+          <t>29281</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46686</t>
+          <t>45625</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,01%</t>
         </is>
       </c>
     </row>
@@ -5276,67 +5276,67 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5379</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>9,58%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>2038</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>5552</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5820</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>3,35%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>9,13%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>5294</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8418</t>
+          <t>8488</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -5384,107 +5384,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3649</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>722</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3988</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3648</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>722</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3643</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -5497,72 +5497,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>1991</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5746</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5516</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>3,27%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,99%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>9,45%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>596</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>5610</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -5610,57 +5610,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>56152</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>56152</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>56152</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>60801</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>60801</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>60801</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>56152</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>56152</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>56152</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5727,72 +5727,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>198830</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>183698</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>213236</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>60,98%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>56,34%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>65,39%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>182306</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>167795</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>195597</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>167469</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>196246</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>58,4%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>53,75%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>62,66%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>198830</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>184673</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>213243</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>60,98%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>360857</t>
+          <t>362233</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>399760</t>
+          <t>401899</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,97%</t>
         </is>
       </c>
     </row>
@@ -5845,67 +5845,67 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>114019</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>100933</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>129241</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>34,97%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>30,95%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>39,64%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
           <t>114874</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>102227</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>129177</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>102397</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>129373</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>36,8%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>32,75%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>41,38%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>114019</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>100268</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>127819</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>34,97%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>209638</t>
+          <t>210547</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>248068</t>
+          <t>248520</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>38,94%</t>
         </is>
       </c>
     </row>
@@ -5958,67 +5958,67 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>9856</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>5936</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>15665</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
           <t>10205</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>6158</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>16443</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>5691</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>16267</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>3,27%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>9856</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>5514</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>15229</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14226</t>
+          <t>13789</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27675</t>
+          <t>28219</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -6066,72 +6066,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1925</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>5135</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>2798</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>7026</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>6948</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,9%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,22%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1925</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>579</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>5468</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9644</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -6179,72 +6179,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1448</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>4738</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>1991</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>592</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5710</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5119</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,64%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1448</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>4481</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7781</t>
+          <t>7992</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -6292,57 +6292,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>326078</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>326078</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>326078</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>444</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>312174</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>312174</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>312174</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>474</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>326078</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>326078</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>326078</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6455,13 +6455,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse alegre en 2016 (tasa de respuesta: 95,77%)</t>
+          <t>Menores según la frecuencia de sentirse alegre, percibida por el/la menor [KIDSCREEN 20] en 2016 (tasa de respuesta: 95,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6472,7 +6472,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6640,72 +6640,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19916</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14333</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>24600</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>54,36%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>39,12%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>67,14%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>17767</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13370</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>22010</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>13071</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>21876</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>58,05%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>43,69%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>71,91%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>19916</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>14910</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>25007</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>54,36%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31391</t>
+          <t>31702</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44511</t>
+          <t>44695</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,47%</t>
         </is>
       </c>
     </row>
@@ -6753,72 +6753,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15282</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10821</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>21208</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>41,71%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>29,54%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>57,89%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>11658</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7162</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>16186</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>7503</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>16457</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>38,09%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>23,4%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>52,88%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>15282</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>10486</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>20797</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>41,71%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20479</t>
+          <t>20804</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33710</t>
+          <t>33380</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>49,64%</t>
         </is>
       </c>
     </row>
@@ -6866,72 +6866,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3933</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>10,73%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1181</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4069</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4165</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>3,86%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>13,3%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>3969</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>569</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -7092,107 +7092,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3950</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>10,78%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>727</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3694</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3620</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>10,08%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>727</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3655</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -7205,57 +7205,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>30606</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>30606</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>30606</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7322,72 +7322,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>143695</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>132524</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>156200</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>60,61%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>55,9%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>65,89%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>147084</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>133773</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>159428</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>134609</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>159614</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>60,28%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>54,83%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>65,34%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>143695</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>129812</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>155767</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>60,61%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>270623</t>
+          <t>271688</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>308661</t>
+          <t>308215</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>64,07%</t>
         </is>
       </c>
     </row>
@@ -7435,72 +7435,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>83799</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>72002</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>95070</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>35,35%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>30,37%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>40,1%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>84508</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>73218</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>98209</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>71904</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>96460</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>34,63%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>30,01%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>40,25%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>83799</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>71934</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>97022</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>35,35%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>151319</t>
+          <t>150554</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>187345</t>
+          <t>186191</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,7%</t>
         </is>
       </c>
     </row>
@@ -7548,72 +7548,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4542</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>14089</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,39%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5,94%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>11124</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6865</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>17514</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>6673</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>17442</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>4,56%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>7,18%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>4175</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>13322</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13694</t>
+          <t>13252</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27965</t>
+          <t>27703</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -7666,102 +7666,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3769</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>524</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2650</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3155</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>759</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1283</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4146</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4553</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1283</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4606</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -7779,102 +7779,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4245</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>759</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4550</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4311</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>764</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3813</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>5339</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>5487</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -7887,57 +7887,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>237063</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>237063</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>237063</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>243998</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>243998</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>243998</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>237063</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>237063</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>237063</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8004,72 +8004,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>47953</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>40882</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>55121</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>63,51%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>54,15%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>73,01%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>39886</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>32245</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>46553</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>33328</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>47146</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>56,11%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>45,36%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>65,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>47953</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>40519</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>55093</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>63,51%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77182</t>
+          <t>78078</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98124</t>
+          <t>98272</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>67,04%</t>
         </is>
       </c>
     </row>
@@ -8117,72 +8117,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>26961</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>20042</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>34295</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>35,71%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>26,55%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>45,42%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>28624</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>21995</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>35851</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>21892</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>35732</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>40,27%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>30,94%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>50,43%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>26961</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>19706</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>34284</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>35,71%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>46146</t>
+          <t>45754</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>66790</t>
+          <t>65985</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,01%</t>
         </is>
       </c>
     </row>
@@ -8230,72 +8230,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2837</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3,76%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>2579</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>6336</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>6142</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>3,63%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>8,91%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>3315</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -8569,57 +8569,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>75502</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>75502</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>75502</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>71090</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>71090</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>71090</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>75502</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>75502</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>75502</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8686,72 +8686,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>211565</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>195841</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>226928</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>60,59%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>56,08%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>64,98%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>293</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>204736</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>190265</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>221744</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>189673</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>218491</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>59,22%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>55,04%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>64,14%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>211565</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>195551</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>226418</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>60,59%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>393387</t>
+          <t>393784</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>437515</t>
+          <t>438145</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>63,05%</t>
         </is>
       </c>
     </row>
@@ -8804,67 +8804,67 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>126042</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>111411</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>142860</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>36,09%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>31,9%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>40,91%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
           <t>124790</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>109274</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>138798</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>110504</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>139981</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>36,1%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>31,61%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>40,15%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>126042</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>112032</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>140237</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>36,09%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>229674</t>
+          <t>230702</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>273356</t>
+          <t>273375</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8912,72 +8912,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>9347</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>5570</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>16190</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>4,64%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>14884</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>9570</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>22042</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>9751</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>22298</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>4,31%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>6,38%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>9347</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>5244</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>15331</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>17328</t>
+          <t>17809</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>34720</t>
+          <t>33515</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -9030,102 +9030,102 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>4278</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
           <t>524</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>2631</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2628</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,15%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>0,76%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>759</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1283</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>3803</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>4599</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1283</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>4647</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -9138,72 +9138,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1490</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>4628</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>759</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>3838</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>4269</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,22%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1490</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>5919</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9223,7 +9223,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -9251,57 +9251,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>493</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>345694</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>345694</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>345694</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
